--- a/output/Pokemon_Portfolio_Intelligence.xlsx
+++ b/output/Pokemon_Portfolio_Intelligence.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PORTFOLIO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EBAY_COMPS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="COLLECTR_MAP" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PSA_MAP" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="INSIGHTS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="EXCEPTIONS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TARGETS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ALERT_LOG" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CONFIG" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTFOLIO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EBAY_COMPS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COLLECTR_MAP" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PSA_MAP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSIGHTS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXCEPTIONS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TARGETS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALERT_LOG" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -210,6 +210,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="002196F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
@@ -221,11 +226,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FF9800"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002196F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -396,16 +396,22 @@
     <xf numFmtId="165" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -427,13 +433,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -840,7 +840,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last Refresh: 2026-04-24 21:00  |  Currency: THB (฿)  |  Rate: 33.22 THB/USD  |  Source: Collectr Live</t>
+          <t>Last Refresh: 2026-04-26 10:49  |  Currency: THB (฿)  |  Rate: 33.22 THB/USD  |  Source: Collectr Live</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -925,17 +925,17 @@
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="11" t="n">
-        <v>195457</v>
+        <v>173132</v>
       </c>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="8" t="n"/>
       <c r="J6" s="12" t="n">
-        <v>43773</v>
+        <v>21448</v>
       </c>
       <c r="K6" s="7" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="13" t="n">
-        <v>0.2886</v>
+        <v>0.1414</v>
       </c>
       <c r="N6" s="7" t="n"/>
       <c r="O6" s="8" t="n"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.1304347826086956</v>
       </c>
       <c r="H10" s="22" t="n"/>
       <c r="I10" s="23" t="inlineStr">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="J10" s="20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O10" s="24" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="C11" s="20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="H11" s="27" t="n"/>
       <c r="I11" s="28" t="inlineStr">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="J11" s="20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O11" s="24" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="J12" s="20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="C13" s="20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="15">
@@ -1178,30 +1178,30 @@
       </c>
       <c r="B17" s="36" t="inlineStr">
         <is>
-          <t>FULL ART/PIKACHU</t>
+          <t>SLOWPOKE</t>
         </is>
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>PSA 10</t>
+          <t>PSA 8</t>
         </is>
       </c>
       <c r="D17" s="36" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>sv1v</t>
         </is>
       </c>
       <c r="E17" s="37" t="n">
-        <v>2558</v>
+        <v>764</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>9966</v>
+        <v>2525</v>
       </c>
       <c r="G17" s="39" t="n">
-        <v>7408</v>
+        <v>1761</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>2.89601250977326</v>
+        <v>2.304973821989529</v>
       </c>
       <c r="I17" s="41" t="inlineStr">
         <is>
@@ -1237,13 +1237,13 @@
         <v>17308</v>
       </c>
       <c r="F18" s="45" t="n">
-        <v>26011</v>
+        <v>24782</v>
       </c>
       <c r="G18" s="39" t="n">
-        <v>8703</v>
+        <v>7474</v>
       </c>
       <c r="H18" s="46" t="n">
-        <v>0.5028310607811417</v>
+        <v>0.4318234342500578</v>
       </c>
       <c r="I18" s="41" t="inlineStr">
         <is>
@@ -1262,39 +1262,39 @@
       </c>
       <c r="B19" s="36" t="inlineStr">
         <is>
-          <t>SLOWPOKE</t>
+          <t>MISCHIEVOUS PICHU</t>
         </is>
       </c>
       <c r="C19" s="36" t="inlineStr">
         <is>
-          <t>PSA 8</t>
+          <t>PSA 10</t>
         </is>
       </c>
       <c r="D19" s="36" t="inlineStr">
         <is>
-          <t>sv1v</t>
+          <t>s-promo</t>
         </is>
       </c>
       <c r="E19" s="37" t="n">
-        <v>764</v>
-      </c>
-      <c r="F19" s="38" t="n">
-        <v>399</v>
-      </c>
-      <c r="G19" s="47" t="n">
-        <v>-365</v>
+        <v>2624</v>
+      </c>
+      <c r="F19" s="37" t="n">
+        <v>3654</v>
+      </c>
+      <c r="G19" s="39" t="n">
+        <v>1030</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>-0.4777486910994764</v>
-      </c>
-      <c r="I19" s="48" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="J19" s="49" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.392530487804878</v>
+      </c>
+      <c r="I19" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J19" s="42" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1304,39 +1304,39 @@
       </c>
       <c r="B20" s="43" t="inlineStr">
         <is>
-          <t>DETECTIVE PIKACHU</t>
+          <t>SNORLAX</t>
         </is>
       </c>
       <c r="C20" s="43" t="inlineStr">
         <is>
-          <t>PSA 10</t>
+          <t>PSA 8</t>
         </is>
       </c>
       <c r="D20" s="43" t="inlineStr">
         <is>
-          <t>sv-p-promo</t>
+          <t>topsun</t>
         </is>
       </c>
       <c r="E20" s="44" t="n">
-        <v>11195</v>
+        <v>9468</v>
       </c>
       <c r="F20" s="45" t="n">
-        <v>15647</v>
-      </c>
-      <c r="G20" s="39" t="n">
-        <v>4452</v>
+        <v>5880</v>
+      </c>
+      <c r="G20" s="48" t="n">
+        <v>-3588</v>
       </c>
       <c r="H20" s="46" t="n">
-        <v>0.3976775346136668</v>
-      </c>
-      <c r="I20" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J20" s="42" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-0.3789607097591888</v>
+      </c>
+      <c r="I20" s="49" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J20" s="50" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B21" s="36" t="inlineStr">
         <is>
-          <t>MISCHIEVOUS PICHU</t>
+          <t>FULL ART/MEW</t>
         </is>
       </c>
       <c r="C21" s="36" t="inlineStr">
@@ -1356,27 +1356,27 @@
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
-          <t>s-promo</t>
+          <t>sword</t>
         </is>
       </c>
       <c r="E21" s="37" t="n">
-        <v>2624</v>
+        <v>4319</v>
       </c>
       <c r="F21" s="37" t="n">
-        <v>3654</v>
-      </c>
-      <c r="G21" s="39" t="n">
-        <v>1030</v>
+        <v>2829</v>
+      </c>
+      <c r="G21" s="48" t="n">
+        <v>-1490</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>0.392530487804878</v>
-      </c>
-      <c r="I21" s="50" t="inlineStr">
+        <v>-0.3449872655707339</v>
+      </c>
+      <c r="I21" s="51" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="J21" s="49" t="inlineStr">
+      <c r="J21" s="50" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1388,39 +1388,39 @@
       </c>
       <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>SNORLAX</t>
+          <t>FULL ART/PIKACHU</t>
         </is>
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
-          <t>PSA 8</t>
+          <t>PSA 10</t>
         </is>
       </c>
       <c r="D22" s="43" t="inlineStr">
         <is>
-          <t>topsun</t>
+          <t>th</t>
         </is>
       </c>
       <c r="E22" s="44" t="n">
-        <v>9468</v>
+        <v>2558</v>
       </c>
       <c r="F22" s="45" t="n">
-        <v>5880</v>
-      </c>
-      <c r="G22" s="47" t="n">
-        <v>-3588</v>
+        <v>3322</v>
+      </c>
+      <c r="G22" s="39" t="n">
+        <v>764</v>
       </c>
       <c r="H22" s="46" t="n">
-        <v>-0.3789607097591888</v>
-      </c>
-      <c r="I22" s="48" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="J22" s="49" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.2986708365910868</v>
+      </c>
+      <c r="I22" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="J22" s="42" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B23" s="36" t="inlineStr">
         <is>
-          <t>FULL ART/MEW</t>
+          <t>PIKACHU</t>
         </is>
       </c>
       <c r="C23" s="36" t="inlineStr">
@@ -1440,27 +1440,27 @@
       </c>
       <c r="D23" s="36" t="inlineStr">
         <is>
-          <t>sword</t>
+          <t>sv2a</t>
         </is>
       </c>
       <c r="E23" s="37" t="n">
-        <v>4319</v>
+        <v>5415</v>
       </c>
       <c r="F23" s="37" t="n">
-        <v>2829</v>
-      </c>
-      <c r="G23" s="47" t="n">
-        <v>-1490</v>
+        <v>4175</v>
+      </c>
+      <c r="G23" s="48" t="n">
+        <v>-1240</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>-0.3449872655707339</v>
-      </c>
-      <c r="I23" s="50" t="inlineStr">
+        <v>-0.2289935364727609</v>
+      </c>
+      <c r="I23" s="51" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="J23" s="49" t="inlineStr">
+      <c r="J23" s="50" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>PIKACHU</t>
+          <t>SNORLAX</t>
         </is>
       </c>
       <c r="C24" s="43" t="inlineStr">
@@ -1482,29 +1482,29 @@
       </c>
       <c r="D24" s="43" t="inlineStr">
         <is>
-          <t>s-promo</t>
+          <t>sv2a</t>
         </is>
       </c>
       <c r="E24" s="44" t="n">
-        <v>10199</v>
+        <v>2990</v>
       </c>
       <c r="F24" s="45" t="n">
-        <v>13122</v>
-      </c>
-      <c r="G24" s="39" t="n">
-        <v>2923</v>
+        <v>2458</v>
+      </c>
+      <c r="G24" s="48" t="n">
+        <v>-532</v>
       </c>
       <c r="H24" s="46" t="n">
-        <v>0.2865967251691342</v>
-      </c>
-      <c r="I24" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J24" s="42" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-0.1779264214046823</v>
+      </c>
+      <c r="I24" s="49" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="J24" s="50" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B25" s="36" t="inlineStr">
         <is>
-          <t>CHARIZARD EX</t>
+          <t>PIKACHU</t>
         </is>
       </c>
       <c r="C25" s="36" t="inlineStr">
@@ -1524,29 +1524,29 @@
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
-          <t>sv4a</t>
+          <t>asia-promo</t>
         </is>
       </c>
       <c r="E25" s="37" t="n">
-        <v>14251</v>
-      </c>
-      <c r="F25" s="38" t="n">
-        <v>18138</v>
-      </c>
-      <c r="G25" s="39" t="n">
-        <v>3887</v>
+        <v>3056</v>
+      </c>
+      <c r="F25" s="37" t="n">
+        <v>2598</v>
+      </c>
+      <c r="G25" s="48" t="n">
+        <v>-458</v>
       </c>
       <c r="H25" s="40" t="n">
-        <v>0.2727527892779454</v>
-      </c>
-      <c r="I25" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J25" s="42" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-0.149869109947644</v>
+      </c>
+      <c r="I25" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J25" s="52" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B26" s="43" t="inlineStr">
         <is>
-          <t>PIKACHU</t>
+          <t>SNORLAX-HOLO</t>
         </is>
       </c>
       <c r="C26" s="43" t="inlineStr">
@@ -1566,29 +1566,29 @@
       </c>
       <c r="D26" s="43" t="inlineStr">
         <is>
-          <t>m-p-promo</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="E26" s="44" t="n">
-        <v>2658</v>
+        <v>7176</v>
       </c>
       <c r="F26" s="45" t="n">
-        <v>3289</v>
-      </c>
-      <c r="G26" s="39" t="n">
-        <v>631</v>
+        <v>6146</v>
+      </c>
+      <c r="G26" s="48" t="n">
+        <v>-1030</v>
       </c>
       <c r="H26" s="46" t="n">
-        <v>0.2373965387509406</v>
-      </c>
-      <c r="I26" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="J26" s="42" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-0.1435340022296544</v>
+      </c>
+      <c r="I26" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J26" s="52" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
           <t>PSA 10</t>
         </is>
       </c>
-      <c r="C30" s="51" t="n">
+      <c r="C30" s="53" t="n">
         <v>30</v>
       </c>
       <c r="D30" s="43" t="inlineStr">
@@ -1661,12 +1661,12 @@
           <t>PSA 10</t>
         </is>
       </c>
-      <c r="C31" s="52" t="n">
-        <v>50</v>
+      <c r="C31" s="54" t="n">
+        <v>70</v>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
-          <t>Low confidence (50%); needs manual verification</t>
+          <t>Slightly underwater: -15.0% (MV 2,598 vs cost 3,056)</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
           <t>PSA 10</t>
         </is>
       </c>
-      <c r="C32" s="51" t="n">
-        <v>50</v>
+      <c r="C32" s="53" t="n">
+        <v>70</v>
       </c>
       <c r="D32" s="43" t="inlineStr">
         <is>
-          <t>Low confidence (50%); needs manual verification</t>
+          <t>Slightly positive: +39.3% (MV 3,654 vs cost 2,624)</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
           <t>PSA 10</t>
         </is>
       </c>
-      <c r="C33" s="52" t="n">
+      <c r="C33" s="54" t="n">
         <v>50</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
@@ -1721,7 +1721,7 @@
           <t>PSA 10</t>
         </is>
       </c>
-      <c r="C34" s="51" t="n">
+      <c r="C34" s="53" t="n">
         <v>30</v>
       </c>
       <c r="D34" s="43" t="inlineStr">
@@ -1741,7 +1741,7 @@
           <t>PSA 10</t>
         </is>
       </c>
-      <c r="C35" s="52" t="n">
+      <c r="C35" s="54" t="n">
         <v>50</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
@@ -1761,7 +1761,7 @@
           <t>PSA 10</t>
         </is>
       </c>
-      <c r="C36" s="51" t="n">
+      <c r="C36" s="53" t="n">
         <v>50</v>
       </c>
       <c r="D36" s="43" t="inlineStr">
@@ -1771,20 +1771,20 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="53" t="inlineStr">
-        <is>
-          <t>✓ LIVE DATA: 16/23 cards priced from Collectr (app.getcollectr.com) as of 2026-04-24 21:00</t>
-        </is>
-      </c>
-      <c r="B38" s="54" t="n"/>
-      <c r="C38" s="54" t="n"/>
-      <c r="D38" s="54" t="n"/>
-      <c r="E38" s="54" t="n"/>
-      <c r="F38" s="54" t="n"/>
-      <c r="G38" s="54" t="n"/>
-      <c r="H38" s="54" t="n"/>
-      <c r="I38" s="54" t="n"/>
-      <c r="J38" s="54" t="n"/>
+      <c r="A38" s="55" t="inlineStr">
+        <is>
+          <t>✓ LIVE DATA: 16/23 cards priced from Collectr (app.getcollectr.com) as of 2026-04-26 10:49</t>
+        </is>
+      </c>
+      <c r="B38" s="56" t="n"/>
+      <c r="C38" s="56" t="n"/>
+      <c r="D38" s="56" t="n"/>
+      <c r="E38" s="56" t="n"/>
+      <c r="F38" s="56" t="n"/>
+      <c r="G38" s="56" t="n"/>
+      <c r="H38" s="56" t="n"/>
+      <c r="I38" s="56" t="n"/>
+      <c r="J38" s="56" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1814,12 +1814,10 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1840,13 +1838,13 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>SYSTEM</t>
         </is>
       </c>
-      <c r="B1" s="59" t="n"/>
-      <c r="C1" s="59" t="n"/>
+      <c r="B1" s="61" t="n"/>
+      <c r="C1" s="61" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="65" t="inlineStr">
@@ -1873,7 +1871,7 @@
       </c>
       <c r="B3" s="66" t="inlineStr">
         <is>
-          <t>2026-04-24 21:00</t>
+          <t>2026-04-26 10:49</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1922,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>CONFIDENCE THRESHOLDS</t>
         </is>
       </c>
-      <c r="B7" s="59" t="n"/>
-      <c r="C7" s="59" t="n"/>
+      <c r="B7" s="61" t="n"/>
+      <c r="C7" s="61" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="65" t="inlineStr">
@@ -1981,13 +1979,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>SIGNAL THRESHOLDS</t>
         </is>
       </c>
-      <c r="B12" s="59" t="n"/>
-      <c r="C12" s="59" t="n"/>
+      <c r="B12" s="61" t="n"/>
+      <c r="C12" s="61" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="65" t="inlineStr">
@@ -2048,13 +2046,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>EBAY PARAMETERS</t>
         </is>
       </c>
-      <c r="B17" s="59" t="n"/>
-      <c r="C17" s="59" t="n"/>
+      <c r="B17" s="61" t="n"/>
+      <c r="C17" s="61" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="65" t="inlineStr">
@@ -2093,13 +2091,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
-      <c r="B21" s="59" t="n"/>
-      <c r="C21" s="59" t="n"/>
+      <c r="B21" s="61" t="n"/>
+      <c r="C21" s="61" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="65" t="inlineStr">
@@ -2131,13 +2129,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="58" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>CACHE</t>
         </is>
       </c>
-      <c r="B24" s="59" t="n"/>
-      <c r="C24" s="59" t="n"/>
+      <c r="B24" s="61" t="n"/>
+      <c r="C24" s="61" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="65" t="inlineStr">
@@ -2164,13 +2162,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>ALERTS (configure here)</t>
         </is>
       </c>
-      <c r="B27" s="59" t="n"/>
-      <c r="C27" s="59" t="n"/>
+      <c r="B27" s="61" t="n"/>
+      <c r="C27" s="61" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="65" t="inlineStr">
@@ -2252,107 +2250,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="D1" s="55" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>Set Code</t>
         </is>
       </c>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>Card #</t>
         </is>
       </c>
-      <c r="F1" s="55" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>Variety</t>
         </is>
       </c>
-      <c r="G1" s="55" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="H1" s="55" t="inlineStr">
+      <c r="H1" s="57" t="inlineStr">
         <is>
           <t>My Cost (THB)</t>
         </is>
       </c>
-      <c r="I1" s="55" t="inlineStr">
+      <c r="I1" s="57" t="inlineStr">
         <is>
           <t>PSA Estimate (THB)</t>
         </is>
       </c>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="J1" s="57" t="inlineStr">
         <is>
           <t>Market Value (THB)</t>
         </is>
       </c>
-      <c r="K1" s="55" t="inlineStr">
+      <c r="K1" s="57" t="inlineStr">
         <is>
           <t>P&amp;L (THB)</t>
         </is>
       </c>
-      <c r="L1" s="55" t="inlineStr">
+      <c r="L1" s="57" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="M1" s="55" t="inlineStr">
+      <c r="M1" s="57" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="N1" s="55" t="inlineStr">
+      <c r="N1" s="57" t="inlineStr">
         <is>
           <t>Liquidity</t>
         </is>
       </c>
-      <c r="O1" s="55" t="inlineStr">
+      <c r="O1" s="57" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="P1" s="55" t="inlineStr">
+      <c r="P1" s="57" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="Q1" s="55" t="inlineStr">
+      <c r="Q1" s="57" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="R1" s="55" t="inlineStr">
+      <c r="R1" s="57" t="inlineStr">
         <is>
           <t>Match Key</t>
         </is>
       </c>
-      <c r="S1" s="55" t="inlineStr">
+      <c r="S1" s="57" t="inlineStr">
         <is>
           <t>Cert Number</t>
         </is>
       </c>
-      <c r="T1" s="55" t="inlineStr">
+      <c r="T1" s="57" t="inlineStr">
         <is>
           <t>Date Acquired</t>
         </is>
       </c>
-      <c r="U1" s="55" t="inlineStr">
+      <c r="U1" s="57" t="inlineStr">
         <is>
           <t>Days Held</t>
         </is>
@@ -2402,7 +2400,7 @@
           <t>131858430</t>
         </is>
       </c>
-      <c r="T2" s="56" t="n">
+      <c r="T2" s="58" t="n">
         <v>46116</v>
       </c>
       <c r="U2" s="43" t="inlineStr"/>
@@ -2451,7 +2449,7 @@
           <t>102808568</t>
         </is>
       </c>
-      <c r="T3" s="57" t="n">
+      <c r="T3" s="59" t="n">
         <v>46116</v>
       </c>
       <c r="U3" s="36" t="inlineStr"/>
@@ -2500,7 +2498,7 @@
           <t>129722527</t>
         </is>
       </c>
-      <c r="T4" s="56" t="n">
+      <c r="T4" s="58" t="n">
         <v>46116</v>
       </c>
       <c r="U4" s="43" t="inlineStr"/>
@@ -2549,7 +2547,7 @@
           <t>105922889</t>
         </is>
       </c>
-      <c r="T5" s="57" t="n">
+      <c r="T5" s="59" t="n">
         <v>46116</v>
       </c>
       <c r="U5" s="36" t="inlineStr"/>
@@ -2594,7 +2592,7 @@
           <t>137306655</t>
         </is>
       </c>
-      <c r="T6" s="56" t="n">
+      <c r="T6" s="58" t="n">
         <v>46116</v>
       </c>
       <c r="U6" s="43" t="inlineStr"/>
@@ -2643,7 +2641,7 @@
           <t>131827338</t>
         </is>
       </c>
-      <c r="T7" s="57" t="n">
+      <c r="T7" s="59" t="n">
         <v>46116</v>
       </c>
       <c r="U7" s="36" t="inlineStr"/>
@@ -2692,7 +2690,7 @@
           <t>124286500</t>
         </is>
       </c>
-      <c r="T8" s="56" t="n">
+      <c r="T8" s="58" t="n">
         <v>46116</v>
       </c>
       <c r="U8" s="43" t="inlineStr"/>
@@ -2741,7 +2739,7 @@
           <t>136143757</t>
         </is>
       </c>
-      <c r="T9" s="57" t="n">
+      <c r="T9" s="59" t="n">
         <v>46116</v>
       </c>
       <c r="U9" s="36" t="inlineStr"/>
@@ -2790,7 +2788,7 @@
           <t>111987130</t>
         </is>
       </c>
-      <c r="T10" s="56" t="n">
+      <c r="T10" s="58" t="n">
         <v>46116</v>
       </c>
       <c r="U10" s="43" t="inlineStr"/>
@@ -2839,7 +2837,7 @@
           <t>133726675</t>
         </is>
       </c>
-      <c r="T11" s="57" t="n">
+      <c r="T11" s="59" t="n">
         <v>46116</v>
       </c>
       <c r="U11" s="36" t="inlineStr"/>
@@ -2888,7 +2886,7 @@
           <t>87561186</t>
         </is>
       </c>
-      <c r="T12" s="56" t="n">
+      <c r="T12" s="58" t="n">
         <v>46117</v>
       </c>
       <c r="U12" s="43" t="inlineStr"/>
@@ -2937,7 +2935,7 @@
           <t>139017599</t>
         </is>
       </c>
-      <c r="T13" s="57" t="n">
+      <c r="T13" s="59" t="n">
         <v>46118</v>
       </c>
       <c r="U13" s="36" t="inlineStr"/>
@@ -2982,7 +2980,7 @@
           <t>131215747</t>
         </is>
       </c>
-      <c r="T14" s="56" t="n">
+      <c r="T14" s="58" t="n">
         <v>46118</v>
       </c>
       <c r="U14" s="43" t="inlineStr"/>
@@ -3031,7 +3029,7 @@
           <t>139442643</t>
         </is>
       </c>
-      <c r="T15" s="57" t="n">
+      <c r="T15" s="59" t="n">
         <v>46120</v>
       </c>
       <c r="U15" s="36" t="inlineStr"/>
@@ -3080,7 +3078,7 @@
           <t>123698796</t>
         </is>
       </c>
-      <c r="T16" s="56" t="n">
+      <c r="T16" s="58" t="n">
         <v>46120</v>
       </c>
       <c r="U16" s="43" t="inlineStr"/>
@@ -3129,7 +3127,7 @@
           <t>124559934</t>
         </is>
       </c>
-      <c r="T17" s="57" t="n">
+      <c r="T17" s="59" t="n">
         <v>46120</v>
       </c>
       <c r="U17" s="36" t="inlineStr"/>
@@ -3225,7 +3223,7 @@
           <t>110351015</t>
         </is>
       </c>
-      <c r="T19" s="57" t="n">
+      <c r="T19" s="59" t="n">
         <v>46123</v>
       </c>
       <c r="U19" s="36" t="inlineStr"/>
@@ -3274,7 +3272,7 @@
           <t>106493053</t>
         </is>
       </c>
-      <c r="T20" s="56" t="n">
+      <c r="T20" s="58" t="n">
         <v>46133</v>
       </c>
       <c r="U20" s="43" t="inlineStr"/>
@@ -3323,7 +3321,7 @@
           <t>118601120</t>
         </is>
       </c>
-      <c r="T21" s="57" t="n">
+      <c r="T21" s="59" t="n">
         <v>46133</v>
       </c>
       <c r="U21" s="36" t="inlineStr"/>
@@ -3462,7 +3460,7 @@
           <t>78726841</t>
         </is>
       </c>
-      <c r="T24" s="56" t="n">
+      <c r="T24" s="58" t="n">
         <v>46136</v>
       </c>
       <c r="U24" s="43" t="inlineStr"/>
@@ -3482,57 +3480,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Match Key</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Comp Title</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Sold Date</t>
         </is>
       </c>
-      <c r="D1" s="55" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>Sold Price (THB)</t>
         </is>
       </c>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>Shipping (THB)</t>
         </is>
       </c>
-      <c r="F1" s="55" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>Total Price (THB)</t>
         </is>
       </c>
-      <c r="G1" s="55" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="H1" s="55" t="inlineStr">
+      <c r="H1" s="57" t="inlineStr">
         <is>
           <t>Comp URL</t>
         </is>
       </c>
-      <c r="I1" s="55" t="inlineStr">
+      <c r="I1" s="57" t="inlineStr">
         <is>
           <t>Is Outlier</t>
         </is>
       </c>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="J1" s="57" t="inlineStr">
         <is>
           <t>Grade Confidence</t>
         </is>
       </c>
-      <c r="K1" s="55" t="inlineStr">
+      <c r="K1" s="57" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3554,37 +3552,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="D1" s="55" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>Collectr URL</t>
         </is>
       </c>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>Collectr Price</t>
         </is>
       </c>
-      <c r="F1" s="55" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="G1" s="55" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Match Confidence</t>
         </is>
@@ -3612,7 +3610,7 @@
         </is>
       </c>
       <c r="E2" s="43" t="n">
-        <v>399</v>
+        <v>2525</v>
       </c>
       <c r="F2" s="43" t="inlineStr">
         <is>
@@ -3645,7 +3643,7 @@
         </is>
       </c>
       <c r="E3" s="36" t="n">
-        <v>3289</v>
+        <v>3056</v>
       </c>
       <c r="F3" s="36" t="inlineStr">
         <is>
@@ -3678,7 +3676,7 @@
         </is>
       </c>
       <c r="E4" s="43" t="n">
-        <v>18138</v>
+        <v>14849</v>
       </c>
       <c r="F4" s="43" t="inlineStr">
         <is>
@@ -3711,7 +3709,7 @@
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>9700</v>
+        <v>8405</v>
       </c>
       <c r="F5" s="36" t="inlineStr">
         <is>
@@ -3744,7 +3742,7 @@
         </is>
       </c>
       <c r="E6" s="43" t="n">
-        <v>9966</v>
+        <v>3322</v>
       </c>
       <c r="F6" s="43" t="inlineStr">
         <is>
@@ -3777,7 +3775,7 @@
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>3289</v>
+        <v>2691</v>
       </c>
       <c r="F7" s="36" t="inlineStr">
         <is>
@@ -3810,7 +3808,7 @@
         </is>
       </c>
       <c r="E8" s="43" t="n">
-        <v>4485</v>
+        <v>3488</v>
       </c>
       <c r="F8" s="43" t="inlineStr">
         <is>
@@ -3870,7 +3868,7 @@
         </is>
       </c>
       <c r="E10" s="43" t="n">
-        <v>26011</v>
+        <v>24782</v>
       </c>
       <c r="F10" s="43" t="inlineStr">
         <is>
@@ -3897,7 +3895,7 @@
           <t>POKEMON ASIA 25TH ANNIVERSARY PROMO</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr"/>
+      <c r="D11" s="36" t="n"/>
       <c r="E11" s="36" t="n">
         <v>2598</v>
       </c>
@@ -3907,7 +3905,7 @@
         </is>
       </c>
       <c r="G11" s="36" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -3932,7 +3930,7 @@
         </is>
       </c>
       <c r="E12" s="43" t="n">
-        <v>15647</v>
+        <v>12723</v>
       </c>
       <c r="F12" s="43" t="inlineStr">
         <is>
@@ -3965,7 +3963,7 @@
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>9136</v>
+        <v>7342</v>
       </c>
       <c r="F13" s="36" t="inlineStr">
         <is>
@@ -3998,7 +3996,7 @@
         </is>
       </c>
       <c r="E14" s="43" t="n">
-        <v>6744</v>
+        <v>6146</v>
       </c>
       <c r="F14" s="43" t="inlineStr">
         <is>
@@ -4031,7 +4029,7 @@
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>3123</v>
+        <v>2458</v>
       </c>
       <c r="F15" s="36" t="inlineStr">
         <is>
@@ -4064,7 +4062,7 @@
         </is>
       </c>
       <c r="E16" s="43" t="n">
-        <v>13122</v>
+        <v>10531</v>
       </c>
       <c r="F16" s="43" t="inlineStr">
         <is>
@@ -4091,7 +4089,7 @@
           <t>POKEMON JAPANESE S PROMO</t>
         </is>
       </c>
-      <c r="D17" s="36" t="inlineStr"/>
+      <c r="D17" s="36" t="n"/>
       <c r="E17" s="36" t="n">
         <v>3654</v>
       </c>
@@ -4101,7 +4099,7 @@
         </is>
       </c>
       <c r="G17" s="36" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
@@ -4159,7 +4157,7 @@
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>24284</v>
+        <v>23985</v>
       </c>
       <c r="F19" s="36" t="inlineStr">
         <is>
@@ -4221,7 +4219,7 @@
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>9700</v>
+        <v>8405</v>
       </c>
       <c r="F21" s="36" t="inlineStr">
         <is>
@@ -4332,42 +4330,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Cert Number</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="D1" s="55" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>Card #</t>
         </is>
       </c>
-      <c r="F1" s="55" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>Variety</t>
         </is>
       </c>
-      <c r="G1" s="55" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="H1" s="55" t="inlineStr">
+      <c r="H1" s="57" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -5171,20 +5169,20 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>TOP UNDERVALUED CARDS</t>
         </is>
       </c>
-      <c r="B1" s="59" t="n"/>
-      <c r="C1" s="59" t="n"/>
-      <c r="D1" s="59" t="n"/>
-      <c r="E1" s="59" t="n"/>
-      <c r="F1" s="59" t="n"/>
-      <c r="G1" s="59" t="n"/>
-      <c r="H1" s="59" t="n"/>
-      <c r="I1" s="59" t="n"/>
-      <c r="J1" s="59" t="n"/>
+      <c r="B1" s="61" t="n"/>
+      <c r="C1" s="61" t="n"/>
+      <c r="D1" s="61" t="n"/>
+      <c r="E1" s="61" t="n"/>
+      <c r="F1" s="61" t="n"/>
+      <c r="G1" s="61" t="n"/>
+      <c r="H1" s="61" t="n"/>
+      <c r="I1" s="61" t="n"/>
+      <c r="J1" s="61" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="35" t="inlineStr">
@@ -5241,30 +5239,30 @@
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
-          <t>FULL ART/PIKACHU</t>
+          <t>SLOWPOKE</t>
         </is>
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>PSA 10</t>
+          <t>PSA 8</t>
         </is>
       </c>
       <c r="C3" s="36" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>sv1v</t>
         </is>
       </c>
       <c r="D3" s="37" t="n">
-        <v>2558</v>
+        <v>764</v>
       </c>
       <c r="E3" s="37" t="n">
-        <v>9966</v>
+        <v>2525</v>
       </c>
       <c r="F3" s="39" t="n">
-        <v>7408</v>
+        <v>1761</v>
       </c>
       <c r="G3" s="40" t="n">
-        <v>2.89601250977326</v>
+        <v>2.304973821989529</v>
       </c>
       <c r="H3" s="36" t="inlineStr">
         <is>
@@ -5278,7 +5276,7 @@
       </c>
       <c r="J3" s="36" t="inlineStr">
         <is>
-          <t>Strong position: +289.6% gain (MV 9,966 vs cost 2,558)</t>
+          <t>Strong position: +230.5% gain (MV 2,525 vs cost 764)</t>
         </is>
       </c>
     </row>
@@ -5302,13 +5300,13 @@
         <v>17308</v>
       </c>
       <c r="E4" s="44" t="n">
-        <v>26011</v>
+        <v>24782</v>
       </c>
       <c r="F4" s="39" t="n">
-        <v>8703</v>
+        <v>7474</v>
       </c>
       <c r="G4" s="46" t="n">
-        <v>0.5028310607811417</v>
+        <v>0.4318234342500578</v>
       </c>
       <c r="H4" s="43" t="inlineStr">
         <is>
@@ -5322,14 +5320,14 @@
       </c>
       <c r="J4" s="43" t="inlineStr">
         <is>
-          <t>Strong position: +50.3% gain (MV 26,011 vs cost 17,308)</t>
+          <t>Strong position: +43.2% gain (MV 24,782 vs cost 17,308)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>DETECTIVE PIKACHU</t>
+          <t>MISCHIEVOUS PICHU</t>
         </is>
       </c>
       <c r="B5" s="36" t="inlineStr">
@@ -5339,41 +5337,41 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>sv-p-promo</t>
+          <t>s-promo</t>
         </is>
       </c>
       <c r="D5" s="37" t="n">
-        <v>11195</v>
+        <v>2624</v>
       </c>
       <c r="E5" s="37" t="n">
-        <v>15647</v>
+        <v>3654</v>
       </c>
       <c r="F5" s="39" t="n">
-        <v>4452</v>
+        <v>1030</v>
       </c>
       <c r="G5" s="40" t="n">
-        <v>0.3976775346136668</v>
+        <v>0.392530487804878</v>
       </c>
       <c r="H5" s="36" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="I5" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I5" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J5" s="36" t="inlineStr">
         <is>
-          <t>Strong position: +39.8% gain (MV 15,647 vs cost 11,195)</t>
+          <t>Slightly positive: +39.3% (MV 3,654 vs cost 2,624)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>MISCHIEVOUS PICHU</t>
+          <t>FULL ART/PIKACHU</t>
         </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
@@ -5383,41 +5381,41 @@
       </c>
       <c r="C6" s="43" t="inlineStr">
         <is>
-          <t>s-promo</t>
+          <t>th</t>
         </is>
       </c>
       <c r="D6" s="44" t="n">
-        <v>2624</v>
+        <v>2558</v>
       </c>
       <c r="E6" s="44" t="n">
-        <v>3654</v>
+        <v>3322</v>
       </c>
       <c r="F6" s="39" t="n">
-        <v>1030</v>
+        <v>764</v>
       </c>
       <c r="G6" s="46" t="n">
-        <v>0.392530487804878</v>
+        <v>0.2986708365910868</v>
       </c>
       <c r="H6" s="43" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="I6" s="50" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I6" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="J6" s="43" t="inlineStr">
         <is>
-          <t>Low confidence (50%); needs manual verification</t>
+          <t>Strong position: +29.9% gain (MV 3,322 vs cost 2,558)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>PIKACHU</t>
+          <t>DETECTIVE PIKACHU</t>
         </is>
       </c>
       <c r="B7" s="36" t="inlineStr">
@@ -5427,52 +5425,52 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>s-promo</t>
+          <t>sv-p-promo</t>
         </is>
       </c>
       <c r="D7" s="37" t="n">
-        <v>10199</v>
+        <v>11195</v>
       </c>
       <c r="E7" s="37" t="n">
-        <v>13122</v>
+        <v>12723</v>
       </c>
       <c r="F7" s="39" t="n">
-        <v>2923</v>
+        <v>1528</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>0.2865967251691342</v>
+        <v>0.1364895042429656</v>
       </c>
       <c r="H7" s="36" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I7" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="I7" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J7" s="36" t="inlineStr">
         <is>
-          <t>Strong position: +28.7% gain (MV 13,122 vs cost 10,199)</t>
+          <t>Slightly positive: +13.6% (MV 12,723 vs cost 11,195)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>STRONGEST GAINERS (by cost basis)</t>
         </is>
       </c>
-      <c r="B9" s="59" t="n"/>
-      <c r="C9" s="59" t="n"/>
-      <c r="D9" s="59" t="n"/>
-      <c r="E9" s="59" t="n"/>
-      <c r="F9" s="59" t="n"/>
-      <c r="G9" s="59" t="n"/>
-      <c r="H9" s="59" t="n"/>
-      <c r="I9" s="59" t="n"/>
-      <c r="J9" s="59" t="n"/>
+      <c r="B9" s="61" t="n"/>
+      <c r="C9" s="61" t="n"/>
+      <c r="D9" s="61" t="n"/>
+      <c r="E9" s="61" t="n"/>
+      <c r="F9" s="61" t="n"/>
+      <c r="G9" s="61" t="n"/>
+      <c r="H9" s="61" t="n"/>
+      <c r="I9" s="61" t="n"/>
+      <c r="J9" s="61" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -5546,27 +5544,27 @@
         <v>22357</v>
       </c>
       <c r="E11" s="37" t="n">
-        <v>24284</v>
+        <v>23985</v>
       </c>
       <c r="F11" s="39" t="n">
-        <v>1927</v>
+        <v>1628</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>0.08619224403989802</v>
+        <v>0.07281835666681576</v>
       </c>
       <c r="H11" s="36" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I11" s="60" t="inlineStr">
+      <c r="I11" s="47" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
       <c r="J11" s="36" t="inlineStr">
         <is>
-          <t>Slightly positive: +8.6% (MV 24,284 vs cost 22,357)</t>
+          <t>Slightly positive: +7.3% (MV 23,985 vs cost 22,357)</t>
         </is>
       </c>
     </row>
@@ -5590,13 +5588,13 @@
         <v>17308</v>
       </c>
       <c r="E12" s="44" t="n">
-        <v>26011</v>
+        <v>24782</v>
       </c>
       <c r="F12" s="39" t="n">
-        <v>8703</v>
+        <v>7474</v>
       </c>
       <c r="G12" s="46" t="n">
-        <v>0.5028310607811417</v>
+        <v>0.4318234342500578</v>
       </c>
       <c r="H12" s="43" t="inlineStr">
         <is>
@@ -5610,7 +5608,7 @@
       </c>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Strong position: +50.3% gain (MV 26,011 vs cost 17,308)</t>
+          <t>Strong position: +43.2% gain (MV 24,782 vs cost 17,308)</t>
         </is>
       </c>
     </row>
@@ -5634,27 +5632,27 @@
         <v>14251</v>
       </c>
       <c r="E13" s="37" t="n">
-        <v>18138</v>
+        <v>14849</v>
       </c>
       <c r="F13" s="39" t="n">
-        <v>3887</v>
+        <v>598</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>0.2727527892779454</v>
+        <v>0.04196196758122237</v>
       </c>
       <c r="H13" s="36" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I13" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="I13" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J13" s="36" t="inlineStr">
         <is>
-          <t>Strong position: +27.3% gain (MV 18,138 vs cost 14,251)</t>
+          <t>Slightly positive: +4.2% (MV 14,849 vs cost 14,251)</t>
         </is>
       </c>
     </row>
@@ -5678,27 +5676,27 @@
         <v>11195</v>
       </c>
       <c r="E14" s="44" t="n">
-        <v>15647</v>
+        <v>12723</v>
       </c>
       <c r="F14" s="39" t="n">
-        <v>4452</v>
+        <v>1528</v>
       </c>
       <c r="G14" s="46" t="n">
-        <v>0.3976775346136668</v>
+        <v>0.1364895042429656</v>
       </c>
       <c r="H14" s="43" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I14" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="I14" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>Strong position: +39.8% gain (MV 15,647 vs cost 11,195)</t>
+          <t>Slightly positive: +13.6% (MV 12,723 vs cost 11,195)</t>
         </is>
       </c>
     </row>
@@ -5722,45 +5720,45 @@
         <v>10199</v>
       </c>
       <c r="E15" s="37" t="n">
-        <v>13122</v>
+        <v>10531</v>
       </c>
       <c r="F15" s="39" t="n">
-        <v>2923</v>
+        <v>332</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>0.2865967251691342</v>
+        <v>0.03255221100107854</v>
       </c>
       <c r="H15" s="36" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I15" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="I15" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J15" s="36" t="inlineStr">
         <is>
-          <t>Strong position: +28.7% gain (MV 13,122 vs cost 10,199)</t>
+          <t>Slightly positive: +3.3% (MV 10,531 vs cost 10,199)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>WEAK POSITIONS</t>
         </is>
       </c>
-      <c r="B17" s="59" t="n"/>
-      <c r="C17" s="59" t="n"/>
-      <c r="D17" s="59" t="n"/>
-      <c r="E17" s="59" t="n"/>
-      <c r="F17" s="59" t="n"/>
-      <c r="G17" s="59" t="n"/>
-      <c r="H17" s="59" t="n"/>
-      <c r="I17" s="59" t="n"/>
-      <c r="J17" s="59" t="n"/>
+      <c r="B17" s="61" t="n"/>
+      <c r="C17" s="61" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="E17" s="61" t="n"/>
+      <c r="F17" s="61" t="n"/>
+      <c r="G17" s="61" t="n"/>
+      <c r="H17" s="61" t="n"/>
+      <c r="I17" s="61" t="n"/>
+      <c r="J17" s="61" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
@@ -5817,7 +5815,7 @@
     <row r="19">
       <c r="A19" s="36" t="inlineStr">
         <is>
-          <t>SLOWPOKE</t>
+          <t>SNORLAX</t>
         </is>
       </c>
       <c r="B19" s="36" t="inlineStr">
@@ -5827,85 +5825,85 @@
       </c>
       <c r="C19" s="36" t="inlineStr">
         <is>
-          <t>sv1v</t>
+          <t>topsun</t>
         </is>
       </c>
       <c r="D19" s="37" t="n">
-        <v>764</v>
+        <v>9468</v>
       </c>
       <c r="E19" s="37" t="n">
-        <v>399</v>
-      </c>
-      <c r="F19" s="47" t="n">
-        <v>-365</v>
+        <v>5880</v>
+      </c>
+      <c r="F19" s="48" t="n">
+        <v>-3588</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>-0.4777486910994764</v>
+        <v>-0.3789607097591888</v>
       </c>
       <c r="H19" s="36" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I19" s="48" t="inlineStr">
+      <c r="I19" s="49" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="J19" s="36" t="inlineStr">
         <is>
-          <t>Underwater: -47.8% loss (MV 399 vs cost 764)</t>
+          <t>Underwater: -37.9% loss (MV 5,880 vs cost 9,468)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="43" t="inlineStr">
         <is>
-          <t>SNORLAX</t>
+          <t>FULL ART/MEW</t>
         </is>
       </c>
       <c r="B20" s="43" t="inlineStr">
         <is>
-          <t>PSA 8</t>
+          <t>PSA 10</t>
         </is>
       </c>
       <c r="C20" s="43" t="inlineStr">
         <is>
-          <t>topsun</t>
+          <t>sword</t>
         </is>
       </c>
       <c r="D20" s="44" t="n">
-        <v>9468</v>
+        <v>4319</v>
       </c>
       <c r="E20" s="44" t="n">
-        <v>5880</v>
-      </c>
-      <c r="F20" s="47" t="n">
-        <v>-3588</v>
+        <v>2829</v>
+      </c>
+      <c r="F20" s="48" t="n">
+        <v>-1490</v>
       </c>
       <c r="G20" s="46" t="n">
-        <v>-0.3789607097591888</v>
+        <v>-0.3449872655707339</v>
       </c>
       <c r="H20" s="43" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="I20" s="48" t="inlineStr">
-        <is>
-          <t>SELL</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I20" s="51" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J20" s="43" t="inlineStr">
         <is>
-          <t>Underwater: -37.9% loss (MV 5,880 vs cost 9,468)</t>
+          <t>Low confidence (50%); needs manual verification</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="36" t="inlineStr">
         <is>
-          <t>FULL ART/MEW</t>
+          <t>PIKACHU</t>
         </is>
       </c>
       <c r="B21" s="36" t="inlineStr">
@@ -5915,27 +5913,27 @@
       </c>
       <c r="C21" s="36" t="inlineStr">
         <is>
-          <t>sword</t>
+          <t>sv2a</t>
         </is>
       </c>
       <c r="D21" s="37" t="n">
-        <v>4319</v>
+        <v>5415</v>
       </c>
       <c r="E21" s="37" t="n">
-        <v>2829</v>
-      </c>
-      <c r="F21" s="47" t="n">
-        <v>-1490</v>
+        <v>4175</v>
+      </c>
+      <c r="F21" s="48" t="n">
+        <v>-1240</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>-0.3449872655707339</v>
+        <v>-0.2289935364727609</v>
       </c>
       <c r="H21" s="36" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="I21" s="50" t="inlineStr">
+      <c r="I21" s="51" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -5949,7 +5947,7 @@
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>PIKACHU</t>
+          <t>SNORLAX</t>
         </is>
       </c>
       <c r="B22" s="43" t="inlineStr">
@@ -5963,30 +5961,30 @@
         </is>
       </c>
       <c r="D22" s="44" t="n">
-        <v>5415</v>
+        <v>2990</v>
       </c>
       <c r="E22" s="44" t="n">
-        <v>4175</v>
-      </c>
-      <c r="F22" s="47" t="n">
-        <v>-1240</v>
+        <v>2458</v>
+      </c>
+      <c r="F22" s="48" t="n">
+        <v>-532</v>
       </c>
       <c r="G22" s="46" t="n">
-        <v>-0.2289935364727609</v>
+        <v>-0.1779264214046823</v>
       </c>
       <c r="H22" s="43" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="I22" s="50" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I22" s="49" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="J22" s="43" t="inlineStr">
         <is>
-          <t>Low confidence (50%); needs manual verification</t>
+          <t>Underwater: -17.8% loss (MV 2,458 vs cost 2,990)</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6010,7 @@
       <c r="E23" s="37" t="n">
         <v>2598</v>
       </c>
-      <c r="F23" s="47" t="n">
+      <c r="F23" s="48" t="n">
         <v>-458</v>
       </c>
       <c r="G23" s="40" t="n">
@@ -6023,55 +6021,55 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="I23" s="50" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
+      <c r="I23" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J23" s="36" t="inlineStr">
         <is>
-          <t>Low confidence (50%); needs manual verification</t>
+          <t>Slightly underwater: -15.0% (MV 2,598 vs cost 3,056)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="58" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>HIGH LIQUIDITY CARDS</t>
         </is>
       </c>
-      <c r="B25" s="59" t="n"/>
-      <c r="C25" s="59" t="n"/>
-      <c r="D25" s="59" t="n"/>
-      <c r="E25" s="59" t="n"/>
-      <c r="F25" s="59" t="n"/>
-      <c r="G25" s="59" t="n"/>
-      <c r="H25" s="59" t="n"/>
-      <c r="I25" s="59" t="n"/>
-      <c r="J25" s="59" t="n"/>
+      <c r="B25" s="61" t="n"/>
+      <c r="C25" s="61" t="n"/>
+      <c r="D25" s="61" t="n"/>
+      <c r="E25" s="61" t="n"/>
+      <c r="F25" s="61" t="n"/>
+      <c r="G25" s="61" t="n"/>
+      <c r="H25" s="61" t="n"/>
+      <c r="I25" s="61" t="n"/>
+      <c r="J25" s="61" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="61" t="inlineStr">
+      <c r="A26" s="62" t="inlineStr">
         <is>
           <t>(No cards in this category)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr">
         <is>
           <t>CARDS NEEDING MANUAL REVIEW</t>
         </is>
       </c>
-      <c r="B28" s="59" t="n"/>
-      <c r="C28" s="59" t="n"/>
-      <c r="D28" s="59" t="n"/>
-      <c r="E28" s="59" t="n"/>
-      <c r="F28" s="59" t="n"/>
-      <c r="G28" s="59" t="n"/>
-      <c r="H28" s="59" t="n"/>
-      <c r="I28" s="59" t="n"/>
-      <c r="J28" s="59" t="n"/>
+      <c r="B28" s="61" t="n"/>
+      <c r="C28" s="61" t="n"/>
+      <c r="D28" s="61" t="n"/>
+      <c r="E28" s="61" t="n"/>
+      <c r="F28" s="61" t="n"/>
+      <c r="G28" s="61" t="n"/>
+      <c r="H28" s="61" t="n"/>
+      <c r="I28" s="61" t="n"/>
+      <c r="J28" s="61" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="35" t="inlineStr">
@@ -6156,7 +6154,7 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="I30" s="50" t="inlineStr">
+      <c r="I30" s="51" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -6180,27 +6178,27 @@
       </c>
       <c r="C31" s="36" t="inlineStr">
         <is>
-          <t>asia-promo</t>
+          <t>sv2a</t>
         </is>
       </c>
       <c r="D31" s="37" t="n">
-        <v>3056</v>
+        <v>5415</v>
       </c>
       <c r="E31" s="37" t="n">
-        <v>2598</v>
-      </c>
-      <c r="F31" s="47" t="n">
-        <v>-458</v>
+        <v>4175</v>
+      </c>
+      <c r="F31" s="48" t="n">
+        <v>-1240</v>
       </c>
       <c r="G31" s="40" t="n">
-        <v>-0.149869109947644</v>
+        <v>-0.2289935364727609</v>
       </c>
       <c r="H31" s="36" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="I31" s="50" t="inlineStr">
+      <c r="I31" s="51" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
@@ -6214,7 +6212,7 @@
     <row r="32">
       <c r="A32" s="43" t="inlineStr">
         <is>
-          <t>MISCHIEVOUS PICHU</t>
+          <t>FUKUOKA'S PIKACHU</t>
         </is>
       </c>
       <c r="B32" s="43" t="inlineStr">
@@ -6224,41 +6222,37 @@
       </c>
       <c r="C32" s="43" t="inlineStr">
         <is>
-          <t>s-promo</t>
-        </is>
-      </c>
-      <c r="D32" s="44" t="n">
-        <v>2624</v>
-      </c>
-      <c r="E32" s="44" t="n">
-        <v>3654</v>
-      </c>
-      <c r="F32" s="39" t="n">
-        <v>1030</v>
+          <t>sv-p-promo</t>
+        </is>
+      </c>
+      <c r="D32" s="44" t="n"/>
+      <c r="E32" s="44" t="n"/>
+      <c r="F32" s="44" t="n">
+        <v>0</v>
       </c>
       <c r="G32" s="46" t="n">
-        <v>0.392530487804878</v>
+        <v>0</v>
       </c>
       <c r="H32" s="43" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="I32" s="50" t="inlineStr">
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I32" s="51" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
       <c r="J32" s="43" t="inlineStr">
         <is>
-          <t>Low confidence (50%); needs manual verification</t>
+          <t>Missing cost or market value</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="36" t="inlineStr">
         <is>
-          <t>PIKACHU</t>
+          <t>MEW EX</t>
         </is>
       </c>
       <c r="B33" s="36" t="inlineStr">
@@ -6268,41 +6262,39 @@
       </c>
       <c r="C33" s="36" t="inlineStr">
         <is>
-          <t>sv2a</t>
-        </is>
-      </c>
-      <c r="D33" s="37" t="n">
-        <v>5415</v>
-      </c>
+          <t>sv4a</t>
+        </is>
+      </c>
+      <c r="D33" s="37" t="n"/>
       <c r="E33" s="37" t="n">
-        <v>4175</v>
-      </c>
-      <c r="F33" s="47" t="n">
-        <v>-1240</v>
+        <v>19288</v>
+      </c>
+      <c r="F33" s="37" t="n">
+        <v>0</v>
       </c>
       <c r="G33" s="40" t="n">
-        <v>-0.2289935364727609</v>
+        <v>0</v>
       </c>
       <c r="H33" s="36" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="I33" s="50" t="inlineStr">
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I33" s="51" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
       <c r="J33" s="36" t="inlineStr">
         <is>
-          <t>Low confidence (50%); needs manual verification</t>
+          <t>Missing cost or market value</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="43" t="inlineStr">
         <is>
-          <t>FUKUOKA'S PIKACHU</t>
+          <t>FULL ART/MEW</t>
         </is>
       </c>
       <c r="B34" s="43" t="inlineStr">
@@ -6312,48 +6304,52 @@
       </c>
       <c r="C34" s="43" t="inlineStr">
         <is>
-          <t>sv-p-promo</t>
-        </is>
-      </c>
-      <c r="D34" s="44" t="n"/>
-      <c r="E34" s="44" t="n"/>
-      <c r="F34" s="44" t="n">
-        <v>0</v>
+          <t>sword</t>
+        </is>
+      </c>
+      <c r="D34" s="44" t="n">
+        <v>4319</v>
+      </c>
+      <c r="E34" s="44" t="n">
+        <v>2829</v>
+      </c>
+      <c r="F34" s="48" t="n">
+        <v>-1490</v>
       </c>
       <c r="G34" s="46" t="n">
-        <v>0</v>
+        <v>-0.3449872655707339</v>
       </c>
       <c r="H34" s="43" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="I34" s="50" t="inlineStr">
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I34" s="51" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
       <c r="J34" s="43" t="inlineStr">
         <is>
-          <t>Missing cost or market value</t>
+          <t>Low confidence (50%); needs manual verification</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>CARDS WITH INSUFFICIENT DATA</t>
         </is>
       </c>
-      <c r="B36" s="59" t="n"/>
-      <c r="C36" s="59" t="n"/>
-      <c r="D36" s="59" t="n"/>
-      <c r="E36" s="59" t="n"/>
-      <c r="F36" s="59" t="n"/>
-      <c r="G36" s="59" t="n"/>
-      <c r="H36" s="59" t="n"/>
-      <c r="I36" s="59" t="n"/>
-      <c r="J36" s="59" t="n"/>
+      <c r="B36" s="61" t="n"/>
+      <c r="C36" s="61" t="n"/>
+      <c r="D36" s="61" t="n"/>
+      <c r="E36" s="61" t="n"/>
+      <c r="F36" s="61" t="n"/>
+      <c r="G36" s="61" t="n"/>
+      <c r="H36" s="61" t="n"/>
+      <c r="I36" s="61" t="n"/>
+      <c r="J36" s="61" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="35" t="inlineStr">
@@ -6427,27 +6423,27 @@
         <v>764</v>
       </c>
       <c r="E38" s="44" t="n">
-        <v>399</v>
-      </c>
-      <c r="F38" s="47" t="n">
-        <v>-365</v>
+        <v>2525</v>
+      </c>
+      <c r="F38" s="39" t="n">
+        <v>1761</v>
       </c>
       <c r="G38" s="46" t="n">
-        <v>-0.4777486910994764</v>
+        <v>2.304973821989529</v>
       </c>
       <c r="H38" s="43" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I38" s="48" t="inlineStr">
-        <is>
-          <t>SELL</t>
+      <c r="I38" s="41" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="J38" s="43" t="inlineStr">
         <is>
-          <t>Underwater: -47.8% loss (MV 399 vs cost 764)</t>
+          <t>Strong position: +230.5% gain (MV 2,525 vs cost 764)</t>
         </is>
       </c>
     </row>
@@ -6471,27 +6467,27 @@
         <v>3089</v>
       </c>
       <c r="E39" s="37" t="n">
-        <v>3289</v>
-      </c>
-      <c r="F39" s="39" t="n">
-        <v>200</v>
+        <v>3056</v>
+      </c>
+      <c r="F39" s="48" t="n">
+        <v>-33</v>
       </c>
       <c r="G39" s="40" t="n">
-        <v>0.06474587245063128</v>
+        <v>-0.01068306895435416</v>
       </c>
       <c r="H39" s="36" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I39" s="60" t="inlineStr">
+      <c r="I39" s="47" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
       <c r="J39" s="36" t="inlineStr">
         <is>
-          <t>Slightly positive: +6.5% (MV 3,289 vs cost 3,089)</t>
+          <t>Slightly underwater: -1.1% (MV 3,056 vs cost 3,089)</t>
         </is>
       </c>
     </row>
@@ -6515,27 +6511,27 @@
         <v>14251</v>
       </c>
       <c r="E40" s="44" t="n">
-        <v>18138</v>
+        <v>14849</v>
       </c>
       <c r="F40" s="39" t="n">
-        <v>3887</v>
+        <v>598</v>
       </c>
       <c r="G40" s="46" t="n">
-        <v>0.2727527892779454</v>
+        <v>0.04196196758122237</v>
       </c>
       <c r="H40" s="43" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I40" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="I40" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J40" s="43" t="inlineStr">
         <is>
-          <t>Strong position: +27.3% gain (MV 18,138 vs cost 14,251)</t>
+          <t>Slightly positive: +4.2% (MV 14,849 vs cost 14,251)</t>
         </is>
       </c>
     </row>
@@ -6559,27 +6555,27 @@
         <v>8139</v>
       </c>
       <c r="E41" s="37" t="n">
-        <v>9700</v>
+        <v>8405</v>
       </c>
       <c r="F41" s="39" t="n">
-        <v>1561</v>
+        <v>266</v>
       </c>
       <c r="G41" s="40" t="n">
-        <v>0.1917926035139452</v>
+        <v>0.03268214768399066</v>
       </c>
       <c r="H41" s="36" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="I41" s="41" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="I41" s="47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J41" s="36" t="inlineStr">
         <is>
-          <t>Strong position: +19.2% gain (MV 9,700 vs cost 8,139)</t>
+          <t>Slightly positive: +3.3% (MV 8,405 vs cost 8,139)</t>
         </is>
       </c>
     </row>
@@ -6603,13 +6599,13 @@
         <v>2558</v>
       </c>
       <c r="E42" s="44" t="n">
-        <v>9966</v>
+        <v>3322</v>
       </c>
       <c r="F42" s="39" t="n">
-        <v>7408</v>
+        <v>764</v>
       </c>
       <c r="G42" s="46" t="n">
-        <v>2.89601250977326</v>
+        <v>0.2986708365910868</v>
       </c>
       <c r="H42" s="43" t="inlineStr">
         <is>
@@ -6623,7 +6619,7 @@
       </c>
       <c r="J42" s="43" t="inlineStr">
         <is>
-          <t>Strong position: +289.6% gain (MV 9,966 vs cost 2,558)</t>
+          <t>Strong position: +29.9% gain (MV 3,322 vs cost 2,558)</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6659,37 +6655,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Match Key</t>
         </is>
       </c>
-      <c r="D1" s="55" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>Card Subject</t>
         </is>
       </c>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>Error Description</t>
         </is>
       </c>
-      <c r="F1" s="55" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="G1" s="55" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Resolution Status</t>
         </is>
@@ -6698,7 +6694,7 @@
     <row r="2">
       <c r="A2" s="43" t="inlineStr">
         <is>
-          <t>2026-04-24 21:00</t>
+          <t>2026-04-26 10:49</t>
         </is>
       </c>
       <c r="B2" s="43" t="inlineStr">
@@ -6713,7 +6709,7 @@
           <t>No market data for PIKACHU</t>
         </is>
       </c>
-      <c r="F2" s="62" t="inlineStr">
+      <c r="F2" s="52" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -6727,7 +6723,7 @@
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
-          <t>2026-04-24 21:00</t>
+          <t>2026-04-26 10:49</t>
         </is>
       </c>
       <c r="B3" s="36" t="inlineStr">
@@ -6742,7 +6738,7 @@
           <t>No market data for FUKUOKA'S PIKACHU</t>
         </is>
       </c>
-      <c r="F3" s="62" t="inlineStr">
+      <c r="F3" s="52" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -6756,7 +6752,7 @@
     <row r="4">
       <c r="A4" s="43" t="inlineStr">
         <is>
-          <t>2026-04-24 21:00</t>
+          <t>2026-04-26 10:49</t>
         </is>
       </c>
       <c r="B4" s="43" t="inlineStr">
@@ -6793,7 +6789,7 @@
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>2026-04-24 21:00</t>
+          <t>2026-04-26 10:49</t>
         </is>
       </c>
       <c r="B5" s="36" t="inlineStr">
@@ -6803,7 +6799,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>pikachu_asia-promo_003_psa10_goldenbox-japanese</t>
+          <t>pikachu_sv2a_173_psa10_artrare</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
@@ -6830,7 +6826,7 @@
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t>2026-04-24 21:00</t>
+          <t>2026-04-26 10:49</t>
         </is>
       </c>
       <c r="B6" s="43" t="inlineStr">
@@ -6840,17 +6836,17 @@
       </c>
       <c r="C6" s="43" t="inlineStr">
         <is>
-          <t>mischievouspichu_s-promo_214_psa10_graniphpurchasecampaign</t>
+          <t>fukuokaspikachu_sv-p-promo_289_psa10_specialboxpokemoncenterfukuoka</t>
         </is>
       </c>
       <c r="D6" s="43" t="inlineStr">
         <is>
-          <t>MISCHIEVOUS PICHU</t>
+          <t>FUKUOKA'S PIKACHU</t>
         </is>
       </c>
       <c r="E6" s="43" t="inlineStr">
         <is>
-          <t>Low match confidence: 50%</t>
+          <t>Low match confidence: 30%</t>
         </is>
       </c>
       <c r="F6" s="43" t="inlineStr">
@@ -6867,7 +6863,7 @@
     <row r="7">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>2026-04-24 21:00</t>
+          <t>2026-04-26 10:49</t>
         </is>
       </c>
       <c r="B7" s="36" t="inlineStr">
@@ -6877,12 +6873,12 @@
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>pikachu_sv2a_173_psa10_artrare</t>
+          <t>mewex_sv4a_347_psa10_specialartrare</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>PIKACHU</t>
+          <t>MEW EX</t>
         </is>
       </c>
       <c r="E7" s="36" t="inlineStr">
@@ -6904,7 +6900,7 @@
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
-          <t>2026-04-24 21:00</t>
+          <t>2026-04-26 10:49</t>
         </is>
       </c>
       <c r="B8" s="43" t="inlineStr">
@@ -6914,17 +6910,17 @@
       </c>
       <c r="C8" s="43" t="inlineStr">
         <is>
-          <t>fukuokaspikachu_sv-p-promo_289_psa10_specialboxpokemoncenterfukuoka</t>
+          <t>fullartmew_sword_183_psa10</t>
         </is>
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t>FUKUOKA'S PIKACHU</t>
+          <t>FULL ART/MEW</t>
         </is>
       </c>
       <c r="E8" s="43" t="inlineStr">
         <is>
-          <t>Low match confidence: 30%</t>
+          <t>Low match confidence: 50%</t>
         </is>
       </c>
       <c r="F8" s="43" t="inlineStr">
@@ -6933,80 +6929,6 @@
         </is>
       </c>
       <c r="G8" s="43" t="inlineStr">
-        <is>
-          <t>Open - needs manual review</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="inlineStr">
-        <is>
-          <t>2026-04-24 21:00</t>
-        </is>
-      </c>
-      <c r="B9" s="36" t="inlineStr">
-        <is>
-          <t>Confidence Check</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>mewex_sv4a_347_psa10_specialartrare</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>MEW EX</t>
-        </is>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>Low match confidence: 50%</t>
-        </is>
-      </c>
-      <c r="F9" s="36" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="G9" s="36" t="inlineStr">
-        <is>
-          <t>Open - needs manual review</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>2026-04-24 21:00</t>
-        </is>
-      </c>
-      <c r="B10" s="43" t="inlineStr">
-        <is>
-          <t>Confidence Check</t>
-        </is>
-      </c>
-      <c r="C10" s="43" t="inlineStr">
-        <is>
-          <t>fullartmew_sword_183_psa10</t>
-        </is>
-      </c>
-      <c r="D10" s="43" t="inlineStr">
-        <is>
-          <t>FULL ART/MEW</t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
-        <is>
-          <t>Low match confidence: 50%</t>
-        </is>
-      </c>
-      <c r="F10" s="43" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="G10" s="43" t="inlineStr">
         <is>
           <t>Open - needs manual review</t>
         </is>
@@ -7040,57 +6962,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Match Key</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="D1" s="55" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>Current Market Value</t>
         </is>
       </c>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>Target Buy Price</t>
         </is>
       </c>
-      <c r="F1" s="55" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>Target Sell Price</t>
         </is>
       </c>
-      <c r="G1" s="55" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Alert Above</t>
         </is>
       </c>
-      <c r="H1" s="55" t="inlineStr">
+      <c r="H1" s="57" t="inlineStr">
         <is>
           <t>Alert Below</t>
         </is>
       </c>
-      <c r="I1" s="55" t="inlineStr">
+      <c r="I1" s="57" t="inlineStr">
         <is>
           <t>Desired Liquidity Min</t>
         </is>
       </c>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="J1" s="57" t="inlineStr">
         <is>
           <t>Active Y/N</t>
         </is>
       </c>
-      <c r="K1" s="55" t="inlineStr">
+      <c r="K1" s="57" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7113,7 +7035,7 @@
         </is>
       </c>
       <c r="D2" s="44" t="n">
-        <v>399</v>
+        <v>2525</v>
       </c>
       <c r="E2" s="63" t="n"/>
       <c r="F2" s="63" t="n"/>
@@ -7144,7 +7066,7 @@
         </is>
       </c>
       <c r="D3" s="37" t="n">
-        <v>3289</v>
+        <v>3056</v>
       </c>
       <c r="E3" s="63" t="n"/>
       <c r="F3" s="63" t="n"/>
@@ -7175,7 +7097,7 @@
         </is>
       </c>
       <c r="D4" s="44" t="n">
-        <v>18138</v>
+        <v>14849</v>
       </c>
       <c r="E4" s="63" t="n"/>
       <c r="F4" s="63" t="n"/>
@@ -7206,7 +7128,7 @@
         </is>
       </c>
       <c r="D5" s="37" t="n">
-        <v>9700</v>
+        <v>8405</v>
       </c>
       <c r="E5" s="63" t="n"/>
       <c r="F5" s="63" t="n"/>
@@ -7237,7 +7159,7 @@
         </is>
       </c>
       <c r="D6" s="44" t="n">
-        <v>9966</v>
+        <v>3322</v>
       </c>
       <c r="E6" s="63" t="n"/>
       <c r="F6" s="63" t="n"/>
@@ -7268,7 +7190,7 @@
         </is>
       </c>
       <c r="D7" s="37" t="n">
-        <v>3289</v>
+        <v>2691</v>
       </c>
       <c r="E7" s="63" t="n"/>
       <c r="F7" s="63" t="n"/>
@@ -7299,7 +7221,7 @@
         </is>
       </c>
       <c r="D8" s="44" t="n">
-        <v>4485</v>
+        <v>3488</v>
       </c>
       <c r="E8" s="63" t="n"/>
       <c r="F8" s="63" t="n"/>
@@ -7359,7 +7281,7 @@
         </is>
       </c>
       <c r="D10" s="44" t="n">
-        <v>26011</v>
+        <v>24782</v>
       </c>
       <c r="E10" s="63" t="n"/>
       <c r="F10" s="63" t="n"/>
@@ -7421,7 +7343,7 @@
         </is>
       </c>
       <c r="D12" s="44" t="n">
-        <v>15647</v>
+        <v>12723</v>
       </c>
       <c r="E12" s="63" t="n"/>
       <c r="F12" s="63" t="n"/>
@@ -7452,7 +7374,7 @@
         </is>
       </c>
       <c r="D13" s="37" t="n">
-        <v>9136</v>
+        <v>7342</v>
       </c>
       <c r="E13" s="63" t="n"/>
       <c r="F13" s="63" t="n"/>
@@ -7483,7 +7405,7 @@
         </is>
       </c>
       <c r="D14" s="44" t="n">
-        <v>6744</v>
+        <v>6146</v>
       </c>
       <c r="E14" s="63" t="n"/>
       <c r="F14" s="63" t="n"/>
@@ -7514,7 +7436,7 @@
         </is>
       </c>
       <c r="D15" s="37" t="n">
-        <v>3123</v>
+        <v>2458</v>
       </c>
       <c r="E15" s="63" t="n"/>
       <c r="F15" s="63" t="n"/>
@@ -7545,7 +7467,7 @@
         </is>
       </c>
       <c r="D16" s="44" t="n">
-        <v>13122</v>
+        <v>10531</v>
       </c>
       <c r="E16" s="63" t="n"/>
       <c r="F16" s="63" t="n"/>
@@ -7638,7 +7560,7 @@
         </is>
       </c>
       <c r="D19" s="37" t="n">
-        <v>24284</v>
+        <v>23985</v>
       </c>
       <c r="E19" s="63" t="n"/>
       <c r="F19" s="63" t="n"/>
@@ -7700,7 +7622,7 @@
         </is>
       </c>
       <c r="D21" s="37" t="n">
-        <v>9700</v>
+        <v>8405</v>
       </c>
       <c r="E21" s="63" t="n"/>
       <c r="F21" s="63" t="n"/>
@@ -7830,49 +7752,49 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Match Key</t>
         </is>
       </c>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Alert Type</t>
         </is>
       </c>
-      <c r="D1" s="55" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>Trigger Value</t>
         </is>
       </c>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="E1" s="57" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="F1" s="55" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>Channel Sent</t>
         </is>
       </c>
-      <c r="G1" s="55" t="inlineStr">
+      <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Delivery Status</t>
         </is>
       </c>
-      <c r="H1" s="55" t="inlineStr">
+      <c r="H1" s="57" t="inlineStr">
         <is>
           <t>Message Preview</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr">
+      <c r="A2" s="62" t="inlineStr">
         <is>
           <t>No alerts triggered yet. Configure targets in the TARGETS sheet.</t>
         </is>
